--- a/xls/square_16_quad4_14.xlsx
+++ b/xls/square_16_quad4_14.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>289</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>432</v>
+      </c>
+      <c r="I12">
+        <v>2.636697860874586</v>
+      </c>
+      <c r="J12">
+        <v>0.34931381563154684</v>
+      </c>
+      <c r="K12">
+        <v>0.8074498272833966</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>507</v>
+      </c>
+      <c r="I13">
+        <v>1.0652885224522413</v>
+      </c>
+      <c r="J13">
+        <v>-0.4900553561530353</v>
+      </c>
+      <c r="K13">
+        <v>0.1260079081870095</v>
+      </c>
+    </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>588</v>
       </c>
       <c r="I14">
-        <v>2.1265189984006603</v>
+        <v>1.4563003977631956</v>
       </c>
       <c r="J14">
-        <v>-0.8894728136595474</v>
+        <v>-1.1061974458012533</v>
       </c>
       <c r="K14">
-        <v>0.125193532363709</v>
+        <v>-0.14798973652264533</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -517,13 +587,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>-1.711759678807396</v>
+        <v>-1.3684102108361462</v>
       </c>
       <c r="J15">
-        <v>-1.7282996436316156</v>
+        <v>-1.4124431262383246</v>
       </c>
       <c r="K15">
-        <v>-1.3661279949086982</v>
+        <v>-1.3183412920853763</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -552,13 +622,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.774141525379413</v>
+        <v>-1.441357807793803</v>
       </c>
       <c r="J16">
-        <v>-1.7941375462272595</v>
+        <v>-1.4969357613734167</v>
       </c>
       <c r="K16">
-        <v>-1.4340059151646014</v>
+        <v>-1.380987566669242</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -587,13 +657,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.8302335630331297</v>
+        <v>-1.487619791092371</v>
       </c>
       <c r="J17">
-        <v>-1.8418789897943115</v>
+        <v>-1.5304017940259835</v>
       </c>
       <c r="K17">
-        <v>-0.7479296866808804</v>
+        <v>1.0899156235664942</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -622,13 +692,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.8771699932289174</v>
+        <v>-1.5509310125154574</v>
       </c>
       <c r="J18">
-        <v>-1.8836569827121294</v>
+        <v>-1.596839994544481</v>
       </c>
       <c r="K18">
-        <v>1.0858063062510266</v>
+        <v>2.254108494323974</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.760852367810955</v>
+        <v>-1.202248210329259</v>
       </c>
       <c r="J19">
-        <v>-1.5452558463688522</v>
+        <v>-1.0285837069028854</v>
       </c>
       <c r="K19">
-        <v>2.6337044958698215</v>
+        <v>4.424359215549887</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.3802696674357045</v>
+        <v>-0.09781575105460638</v>
       </c>
       <c r="J20">
-        <v>-1.0792136160107249</v>
+        <v>-0.09785668378486555</v>
       </c>
       <c r="K20">
-        <v>3.639512561985178</v>
+        <v>4.788962465690495</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-0.5561279458181866</v>
+        <v>-0.016224782820816474</v>
       </c>
       <c r="J21">
-        <v>-0.5265491000454627</v>
+        <v>-0.015620586383392802</v>
       </c>
       <c r="K21">
-        <v>3.915536792602863</v>
+        <v>4.452126114632345</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.1290509231592255</v>
+        <v>-0.001269600676504266</v>
       </c>
       <c r="J22">
-        <v>-0.12343222357111656</v>
+        <v>-0.0012051637659256772</v>
       </c>
       <c r="K22">
-        <v>3.8591191171752266</v>
+        <v>3.9307900549242447</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.06239732039022095</v>
+        <v>-0.0004456096747308645</v>
       </c>
       <c r="J23">
-        <v>-0.06370457741697773</v>
+        <v>-0.0004471812258215754</v>
       </c>
       <c r="K23">
-        <v>3.806324096328524</v>
+        <v>3.7122477339833324</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.0033155472409615136</v>
+        <v>-3.232217743524432e-5</v>
       </c>
       <c r="J24">
-        <v>-0.0028379341763772824</v>
+        <v>-2.7758077365115837e-5</v>
       </c>
       <c r="K24">
-        <v>3.146435996812336</v>
+        <v>3.1046199006842476</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -867,13 +937,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.009251333845422965</v>
+        <v>-5.402917514705805e-5</v>
       </c>
       <c r="J25">
-        <v>-0.007781578874396582</v>
+        <v>-4.586315274367135e-5</v>
       </c>
       <c r="K25">
-        <v>3.3600008837528774</v>
+        <v>3.204731420345624</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.0024227313785201918</v>
+        <v>-1.744644586798377e-5</v>
       </c>
       <c r="J26">
-        <v>-0.002297464572237395</v>
+        <v>-1.6615614104979385e-5</v>
       </c>
       <c r="K26">
-        <v>3.122493303254767</v>
+        <v>3.017729318841201</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>3.67403669191947e-6</v>
+        <v>1.7909497247035678e-8</v>
       </c>
       <c r="J27">
-        <v>3.075261050004416e-8</v>
+        <v>-1.3307119478837763e-8</v>
       </c>
       <c r="K27">
-        <v>1.776629417918044</v>
+        <v>1.7833618479369986</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-1.1350462501439754e-5</v>
+        <v>-1.6341730996673993e-7</v>
       </c>
       <c r="J28">
-        <v>-9.432346571469262e-6</v>
+        <v>-1.4447509076553542e-7</v>
       </c>
       <c r="K28">
-        <v>1.883902808875991</v>
+        <v>1.9696677988487503</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-3.6061314929719134e-7</v>
+        <v>-6.3820519120018725e-9</v>
       </c>
       <c r="J29">
-        <v>-6.578975871320533e-7</v>
+        <v>-1.1541127396917721e-8</v>
       </c>
       <c r="K29">
-        <v>1.4519254686413328</v>
+        <v>1.539047938936374</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-1.2576136466252225e-6</v>
+        <v>-1.7520626023898835e-8</v>
       </c>
       <c r="J30">
-        <v>-1.0678202778429858e-6</v>
+        <v>-1.562103956081477e-8</v>
       </c>
       <c r="K30">
-        <v>1.4178527435835082</v>
+        <v>1.4849112652823908</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-1.8310318882198465e-6</v>
+        <v>-2.4856886253920816e-8</v>
       </c>
       <c r="J31">
-        <v>-1.3773239713649826e-6</v>
+        <v>-1.9277957938719332e-8</v>
       </c>
       <c r="K31">
-        <v>1.424812974983982</v>
+        <v>1.4842041533761596</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1112,13 +1182,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-9.652281808539096e-7</v>
+        <v>-1.301144707357525e-8</v>
       </c>
       <c r="J32">
-        <v>-8.511913444440919e-7</v>
+        <v>-1.1802438980388591e-8</v>
       </c>
       <c r="K32">
-        <v>1.3814726790713454</v>
+        <v>1.4274019045210895</v>
       </c>
     </row>
   </sheetData>
